--- a/legal_forms/046_restraining_order_service_status_form--legal_forms.xlsx
+++ b/legal_forms/046_restraining_order_service_status_form--legal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -965,12 +965,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>service_level</t>
+          <t>service_level_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Service Level</t>
+          <t>Service Level 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>date_of_filing</t>
+          <t>date_of_filing_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Date of Filing</t>
+          <t>Date Of Filing 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>date_of_disposition</t>
+          <t>date_of_disposition_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Date of Disposition</t>
+          <t>Date Of Disposition 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>case_manager_notes</t>
+          <t>case_manager_notes_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Case Manager Notes</t>
+          <t>Case Manager Notes 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>service_level_choices</t>
+          <t>service_level_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>service_level_choices</t>
+          <t>service_level_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>service_level_choices</t>
+          <t>service_level_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
